--- a/docs/agile/Unit_Test_Plan_v0.1.xlsx
+++ b/docs/agile/Unit_Test_Plan_v0.1.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" min="1" max="1"/>
@@ -866,6 +866,186 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Relevance Agent - Category Classification</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mock LLM returns fully_relevant category, call RelevanceJudgeAgent.evaluate()</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LLM returns valid category from defined scale</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Parsed category matches mock value, invalid categories rejected</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Accuracy Agent - Multi-claim Partial Correctness</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Response with one correct claim + one incorrect claim (e.g. correct capital, wrong population)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Response contains multiple substantive claims</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Category = partially_correct, not incorrect</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>As expected (fixed after M2.4 validation found mismatch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hallucination Agent - Claim-level Evidence</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mock LLM returns claims array with per-claim evidence and reason</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Response has one unsupported claim among supported ones</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>claim_evidence populated with claim text, evidence snippet, and reason; hallucination_status = partial</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hallucination Agent - Irrelevant Response Not Flagged</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Response is off-topic (doesn't attempt to answer)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Response has no connection to the question</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>hallucination_status = none, not flagged as hallucination merely for lacking evidence coverage</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>As expected (fixed after M2.4 validation found mismatch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Relevance Agent - Unrelated vs Off-topic Distinction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Response about general topic (France cuisine) vs completely unconnected response (chess)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Two distinct relevance failure modes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>unrelated for same-topic-wrong-answer, off_topic for no-connection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>As expected (fixed after M2.4 validation found mismatch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M2.4 Validation Suite - Full Run</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8 curated cases (correct, incorrect, partially_correct, irrelevant, off_topic, incomplete, unsupported_claim, no_reference) run through real Gemini agents</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Live Gemini API calls, RPM-limited to 15/min</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0 mismatches against expected category across 22 real evaluation calls</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PASSED - 0/22 mismatches</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/docs/agile/Unit_Test_Plan_v0.1.xlsx
+++ b/docs/agile/Unit_Test_Plan_v0.1.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" min="1" max="1"/>
@@ -1046,6 +1046,546 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Completeness Agent - Aspect Breakdown</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mock LLM returns addressed_aspects and missing_aspects arrays, call CompletenessJudgeAgent.evaluate()</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Response addresses some but not all sub-requirements of the question</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>addressed_aspects and missing_aspects populated correctly; category derived as complete/mostly_complete/incomplete</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Verdict Agent - Pass/Needs Improvement/Fail Labeling</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VerdictAgent.aggregate() across PASS/PARTIAL/FAIL score combinations</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>overall_score crossing each threshold boundary</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>verdict_label returns 'Pass', 'Needs Improvement', or 'Fail' matching the internal verdict</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Verdict Agent - Severe Hallucination Override</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VerdictAgent.aggregate() with hallucination_status='full' but otherwise high scores</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Full hallucination detected despite good relevance/accuracy/completeness scores</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>verdict forced to FAIL regardless of weighted average</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Verdict Agent - Missing Aspects Reported</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VerdictAgent.aggregate() with completeness.missing_aspects populated</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Completeness judge found missing aspects</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>major_issues includes missing-aspect entry; improvement_suggestions includes matching suggestion</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M3.3 Frontend - Correct Response Scenario</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Manual test: submit correct Paris answer via frontend</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fully correct, relevant, complete response</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Hero verdict shows Pass, all 4 metric tiles green, 'No unsupported claims detected' empty state shown</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>As expected (manually verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M3.3 Frontend - Hallucinated Response Scenario</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Manual test: submit incorrect Berlin answer via frontend</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Response contradicts retrieved evidence</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Hero verdict shows Fail, Hallucination Investigation panel shows claim cards tagged 'contradicted', evidence displayed per claim</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>As expected (manually verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M3.3 Frontend - Partially Complete Response Scenario</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Manual test: submit partially complete primary-colors answer via frontend</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Response omits part of what was asked</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Hero verdict shows Needs Improvement, Completeness panel lists missing aspects clearly</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>As expected (manually verified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M3.4 CSV Parser - Valid Multi-record CSV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>parse_batch_csv() with a well-formed CSV containing multiple valid rows</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>All required columns present, all required fields populated</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>All rows returned as valid_rows, zero invalid_rows</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M3.4 CSV Parser - Missing Required Column</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>parse_batch_csv() with a CSV missing the ai_response column</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Required column absent from header</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>header_error returned naming the missing column; no rows processed</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M3.4 CSV Parser - Empty Required Field</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>parse_batch_csv() with rows containing blank question or ai_response</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Required field present in header but blank in a data row</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Row reported in invalid_rows with reason naming the missing field(s); does not raise an exception</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M3.4 CSV Parser - Malformed/Short Row</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>parse_batch_csv() with a row having fewer columns than the header</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ragged CSV row</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Row correctly treated as missing the absent field(s) and reported invalid; no crash</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M3.4 CSV Parser - Optional Fields Blank</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>parse_batch_csv() with reference_answer/source_document left blank</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Optional columns present but empty</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Row is valid; optional fields resolve to None, not an error</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M3.4 Batch Service - One Row Failure Does Not Stop Batch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mock orchestrator to raise an exception on row 2 of 3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Simulated LLM/orchestrator failure mid-batch</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Row 2 recorded with an error field; rows 1 and 3 still evaluated successfully</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M3.4 Batch Service - Aggregate Statistics</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>compute_summary() over a mix of passing, failing, and errored records</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Records with varied verdicts and one evaluation failure</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>total/valid/invalid/evaluated/failed counts, per-dimension averages, verdict counts, and hallucination_frequency all computed correctly</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M3.4 API Endpoint - Rejects Non-CSV File</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>POST /evaluate/batch with a .txt file</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Uploaded file is not a CSV</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>400 response with a clear error message</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M3.4 API Endpoint - Rejects Missing Required Column</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>POST /evaluate/batch with a CSV missing ai_response column</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Header-level validation failure</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>400 response naming the missing column</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M3.4 API Endpoint - Full Batch Stream</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>POST /evaluate/batch with a mixed valid/invalid CSV, mocked orchestrator</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>One valid row, one invalid row</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NDJSON stream includes init (correct valid/invalid counts), one progress message with a populated result, and a summary message with correct evaluated/invalid counts</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M3.4 Frontend - End-to-End Batch Upload (Manual)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Manual test: upload a 5-row CSV (4 valid, 1 missing ai_response) via the batch upload UI</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mixed valid/invalid CSV uploaded through the browser</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Invalid row reported as 'Row 5: Missing required field(s): ai_response'; batch did not stop; all 4 valid rows evaluated (Pass/Fail/Needs Improvement outcomes observed); aggregate statistics and per-row table displayed; 'View' buttons opened correct individual results</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>As expected (manually verified)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
